--- a/Entrega_6/fuerzas_por_pier.xlsx
+++ b/Entrega_6/fuerzas_por_pier.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e453337d7bb58d0d/Escritorio/Semestre XI/Proyecto Civil/Proyecto_civil/Entrega_6/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_23F921EDF1638C07032C4C7CCD8BCA517C28768F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8A062B4-3886-40CB-AD6B-9AC787D8DB52}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="9495" yWindow="0" windowWidth="9810" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -196,8 +202,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,13 +266,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -304,7 +318,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -338,6 +352,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -372,9 +387,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -546,12 +562,34 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{35082370-1E4C-403C-94FD-4A8B23CF4503}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;ce243562-298f-437a-822f-f06b54ea16e2&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,12 +699,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
       <c r="B2">
-        <v>47.44232519531948</v>
+        <v>47.442325195319476</v>
       </c>
       <c r="C2">
         <v>0.2</v>
@@ -675,103 +713,103 @@
         <v>57</v>
       </c>
       <c r="E2">
-        <v>90.758</v>
+        <v>90.757999999999996</v>
       </c>
       <c r="F2">
-        <v>80.93170000000001</v>
+        <v>80.931700000000006</v>
       </c>
       <c r="G2">
-        <v>105.4009</v>
+        <v>105.40089999999999</v>
       </c>
       <c r="H2">
-        <v>210.3668</v>
+        <v>210.36680000000001</v>
       </c>
       <c r="I2">
-        <v>90.758</v>
+        <v>90.757999999999996</v>
       </c>
       <c r="J2">
-        <v>80.93170000000001</v>
+        <v>80.931700000000006</v>
       </c>
       <c r="K2">
-        <v>105.4009</v>
+        <v>105.40089999999999</v>
       </c>
       <c r="L2">
-        <v>210.3668</v>
+        <v>210.36680000000001</v>
       </c>
       <c r="M2">
-        <v>310.252</v>
+        <v>310.25200000000001</v>
       </c>
       <c r="N2">
-        <v>294.5399</v>
+        <v>294.53989999999999</v>
       </c>
       <c r="O2">
-        <v>294.3905</v>
+        <v>294.39049999999997</v>
       </c>
       <c r="P2">
-        <v>403.9666</v>
+        <v>403.96660000000003</v>
       </c>
       <c r="Q2">
-        <v>74.2811</v>
+        <v>74.281099999999995</v>
       </c>
       <c r="R2">
-        <v>84.11750000000001</v>
+        <v>84.117500000000007</v>
       </c>
       <c r="S2">
-        <v>87.9462</v>
+        <v>87.946200000000005</v>
       </c>
       <c r="T2">
-        <v>143.8221</v>
+        <v>143.82210000000001</v>
       </c>
       <c r="U2">
-        <v>-41.5256</v>
+        <v>-41.525599999999997</v>
       </c>
       <c r="V2">
         <v>-39.1494</v>
       </c>
       <c r="W2">
-        <v>5.0862</v>
+        <v>5.0861999999999998</v>
       </c>
       <c r="X2">
-        <v>5.5207</v>
+        <v>5.5206999999999997</v>
       </c>
       <c r="Y2">
-        <v>-103.2006</v>
+        <v>-103.20059999999999</v>
       </c>
       <c r="Z2">
         <v>-39.1494</v>
       </c>
       <c r="AA2">
-        <v>5.0862</v>
+        <v>5.0861999999999998</v>
       </c>
       <c r="AB2">
-        <v>5.5207</v>
+        <v>5.5206999999999997</v>
       </c>
       <c r="AC2">
-        <v>171.6897</v>
+        <v>171.68969999999999</v>
       </c>
       <c r="AD2">
-        <v>604.7918999999999</v>
+        <v>604.79189999999994</v>
       </c>
       <c r="AE2">
         <v>309.231875</v>
       </c>
       <c r="AF2">
-        <v>834.131875</v>
+        <v>834.13187500000004</v>
       </c>
       <c r="AG2">
-        <v>4.401328013073892</v>
+        <v>4.4013280130738917</v>
       </c>
       <c r="AH2">
-        <v>5.233534945783825</v>
+        <v>5.2335349457838252</v>
       </c>
       <c r="AI2">
-        <v>4.401328013071556</v>
+        <v>4.4013280130715557</v>
       </c>
       <c r="AJ2">
-        <v>52.67586014110331</v>
+        <v>52.675860141103307</v>
       </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -788,100 +826,100 @@
         <v>-21.5459</v>
       </c>
       <c r="F3">
-        <v>-23.4705</v>
+        <v>-23.470500000000001</v>
       </c>
       <c r="G3">
-        <v>156.9326</v>
+        <v>156.93260000000001</v>
       </c>
       <c r="H3">
-        <v>34.6338</v>
+        <v>34.633800000000001</v>
       </c>
       <c r="I3">
         <v>-21.5459</v>
       </c>
       <c r="J3">
-        <v>-23.4705</v>
+        <v>-23.470500000000001</v>
       </c>
       <c r="K3">
-        <v>156.9326</v>
+        <v>156.93260000000001</v>
       </c>
       <c r="L3">
-        <v>34.6338</v>
+        <v>34.633800000000001</v>
       </c>
       <c r="M3">
-        <v>27.3762</v>
+        <v>27.376200000000001</v>
       </c>
       <c r="N3">
-        <v>28.6637</v>
+        <v>28.663699999999999</v>
       </c>
       <c r="O3">
         <v>273.4855</v>
       </c>
       <c r="P3">
-        <v>68.2735</v>
+        <v>68.273499999999999</v>
       </c>
       <c r="Q3">
         <v>-28.6432</v>
       </c>
       <c r="R3">
-        <v>-32.3595</v>
+        <v>-32.359499999999997</v>
       </c>
       <c r="S3">
-        <v>134.7712</v>
+        <v>134.77119999999999</v>
       </c>
       <c r="T3">
-        <v>34.489</v>
+        <v>34.488999999999997</v>
       </c>
       <c r="U3">
         <v>-36.7532</v>
       </c>
       <c r="V3">
-        <v>-35.1075</v>
+        <v>-35.107500000000002</v>
       </c>
       <c r="W3">
-        <v>3.1064</v>
+        <v>3.1063999999999998</v>
       </c>
       <c r="X3">
         <v>12.2056</v>
       </c>
       <c r="Y3">
-        <v>-70.81319999999999</v>
+        <v>-70.813199999999995</v>
       </c>
       <c r="Z3">
-        <v>-35.1075</v>
+        <v>-35.107500000000002</v>
       </c>
       <c r="AA3">
-        <v>3.1064</v>
+        <v>3.1063999999999998</v>
       </c>
       <c r="AB3">
         <v>12.2056</v>
       </c>
       <c r="AC3">
-        <v>-45.0164</v>
+        <v>-45.016399999999997</v>
       </c>
       <c r="AD3">
-        <v>56.0399</v>
+        <v>56.039900000000003</v>
       </c>
       <c r="AE3">
         <v>-178.4785</v>
       </c>
       <c r="AF3">
-        <v>300.8617</v>
+        <v>300.86169999999998</v>
       </c>
       <c r="AG3">
-        <v>4.401328013071556</v>
+        <v>4.4013280130715557</v>
       </c>
       <c r="AH3">
-        <v>52.67586014110331</v>
+        <v>52.675860141103307</v>
       </c>
       <c r="AI3">
-        <v>30.60132801306612</v>
+        <v>30.601328013066119</v>
       </c>
       <c r="AJ3">
-        <v>52.67586014110381</v>
+        <v>52.675860141103811</v>
       </c>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -895,108 +933,108 @@
         <v>57</v>
       </c>
       <c r="E4">
-        <v>-19.9414</v>
+        <v>-19.941400000000002</v>
       </c>
       <c r="F4">
         <v>-11.4693</v>
       </c>
       <c r="G4">
-        <v>77.86660000000001</v>
+        <v>77.866600000000005</v>
       </c>
       <c r="H4">
-        <v>190.2291</v>
+        <v>190.22909999999999</v>
       </c>
       <c r="I4">
-        <v>-19.9414</v>
+        <v>-19.941400000000002</v>
       </c>
       <c r="J4">
         <v>-11.4693</v>
       </c>
       <c r="K4">
-        <v>77.86660000000001</v>
+        <v>77.866600000000005</v>
       </c>
       <c r="L4">
-        <v>190.2291</v>
+        <v>190.22909999999999</v>
       </c>
       <c r="M4">
-        <v>52.6255</v>
+        <v>52.625500000000002</v>
       </c>
       <c r="N4">
-        <v>36.2713</v>
+        <v>36.271299999999997</v>
       </c>
       <c r="O4">
         <v>147.5598</v>
       </c>
       <c r="P4">
-        <v>401.1794</v>
+        <v>401.17939999999999</v>
       </c>
       <c r="Q4">
-        <v>0.7779</v>
+        <v>0.77790000000000004</v>
       </c>
       <c r="R4">
-        <v>6.4511</v>
+        <v>6.4511000000000003</v>
       </c>
       <c r="S4">
-        <v>57.8965</v>
+        <v>57.896500000000003</v>
       </c>
       <c r="T4">
-        <v>93.4796</v>
+        <v>93.479600000000005</v>
       </c>
       <c r="U4">
-        <v>-39.3749</v>
+        <v>-39.374899999999997</v>
       </c>
       <c r="V4">
-        <v>-38.2734</v>
+        <v>-38.273400000000002</v>
       </c>
       <c r="W4">
-        <v>21.565</v>
+        <v>21.565000000000001</v>
       </c>
       <c r="X4">
-        <v>7.682</v>
+        <v>7.6820000000000004</v>
       </c>
       <c r="Y4">
-        <v>-78.6609</v>
+        <v>-78.660899999999998</v>
       </c>
       <c r="Z4">
-        <v>-38.2734</v>
+        <v>-38.273400000000002</v>
       </c>
       <c r="AA4">
-        <v>21.565</v>
+        <v>21.565000000000001</v>
       </c>
       <c r="AB4">
-        <v>7.682</v>
+        <v>7.6820000000000004</v>
       </c>
       <c r="AC4">
-        <v>-31.4107</v>
+        <v>-31.410699999999999</v>
       </c>
       <c r="AD4">
-        <v>88.8968</v>
+        <v>88.896799999999999</v>
       </c>
       <c r="AE4">
         <v>-210.1705</v>
       </c>
       <c r="AF4">
-        <v>453.8049</v>
+        <v>453.80489999999998</v>
       </c>
       <c r="AG4">
-        <v>30.60132801306612</v>
+        <v>30.601328013066119</v>
       </c>
       <c r="AH4">
-        <v>52.67586014110381</v>
+        <v>52.675860141103811</v>
       </c>
       <c r="AI4">
-        <v>30.60132801307095</v>
+        <v>30.601328013070951</v>
       </c>
       <c r="AJ4">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5">
-        <v>3.349999999998541</v>
+        <v>3.3499999999985408</v>
       </c>
       <c r="C5">
         <v>0.2</v>
@@ -1008,105 +1046,105 @@
         <v>4.8445</v>
       </c>
       <c r="F5">
-        <v>4.7552</v>
+        <v>4.7552000000000003</v>
       </c>
       <c r="G5">
-        <v>37.2225</v>
+        <v>37.222499999999997</v>
       </c>
       <c r="H5">
-        <v>1.513</v>
+        <v>1.5129999999999999</v>
       </c>
       <c r="I5">
         <v>4.8445</v>
       </c>
       <c r="J5">
-        <v>4.7552</v>
+        <v>4.7552000000000003</v>
       </c>
       <c r="K5">
-        <v>37.2225</v>
+        <v>37.222499999999997</v>
       </c>
       <c r="L5">
-        <v>1.513</v>
+        <v>1.5129999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1901</v>
+        <v>0.19009999999999999</v>
       </c>
       <c r="N5">
         <v>1.998</v>
       </c>
       <c r="O5">
-        <v>52.4353</v>
+        <v>52.435299999999998</v>
       </c>
       <c r="P5">
-        <v>4.9768</v>
+        <v>4.9767999999999999</v>
       </c>
       <c r="Q5">
         <v>-12.4054</v>
       </c>
       <c r="R5">
-        <v>-10.3655</v>
+        <v>-10.365500000000001</v>
       </c>
       <c r="S5">
-        <v>44.3528</v>
+        <v>44.352800000000002</v>
       </c>
       <c r="T5">
-        <v>3.7109</v>
+        <v>3.7109000000000001</v>
       </c>
       <c r="U5">
         <v>-11.7676</v>
       </c>
       <c r="V5">
-        <v>-8.484500000000001</v>
+        <v>-8.4845000000000006</v>
       </c>
       <c r="W5">
-        <v>2.8755</v>
+        <v>2.8755000000000002</v>
       </c>
       <c r="X5">
-        <v>3.2613</v>
+        <v>3.2612999999999999</v>
       </c>
       <c r="Y5">
-        <v>-16.1226</v>
+        <v>-16.122599999999998</v>
       </c>
       <c r="Z5">
-        <v>-8.484500000000001</v>
+        <v>-8.4845000000000006</v>
       </c>
       <c r="AA5">
-        <v>2.8755</v>
+        <v>2.8755000000000002</v>
       </c>
       <c r="AB5">
-        <v>3.2613</v>
+        <v>3.2612999999999999</v>
       </c>
       <c r="AC5">
-        <v>9.5997</v>
+        <v>9.5997000000000003</v>
       </c>
       <c r="AD5">
-        <v>2.1881</v>
+        <v>2.1880999999999999</v>
       </c>
       <c r="AE5">
-        <v>42.06699999999999</v>
+        <v>42.066999999999993</v>
       </c>
       <c r="AF5">
-        <v>52.6254</v>
+        <v>52.625399999999999</v>
       </c>
       <c r="AG5">
-        <v>30.60132801307095</v>
+        <v>30.601328013070951</v>
       </c>
       <c r="AH5">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AI5">
         <v>27.25132801307241</v>
       </c>
       <c r="AJ5">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>40</v>
       </c>
       <c r="B6">
-        <v>9.495403058547366</v>
+        <v>9.4954030585473657</v>
       </c>
       <c r="C6">
         <v>0.2</v>
@@ -1118,49 +1156,49 @@
         <v>-14.301</v>
       </c>
       <c r="F6">
-        <v>-8.932499999999999</v>
+        <v>-8.9324999999999992</v>
       </c>
       <c r="G6">
-        <v>17.287</v>
+        <v>17.286999999999999</v>
       </c>
       <c r="H6">
-        <v>58.8195</v>
+        <v>58.819499999999998</v>
       </c>
       <c r="I6">
         <v>-14.301</v>
       </c>
       <c r="J6">
-        <v>-8.932499999999999</v>
+        <v>-8.9324999999999992</v>
       </c>
       <c r="K6">
-        <v>17.287</v>
+        <v>17.286999999999999</v>
       </c>
       <c r="L6">
-        <v>58.8195</v>
+        <v>58.819499999999998</v>
       </c>
       <c r="M6">
         <v>106.985</v>
       </c>
       <c r="N6">
-        <v>50.3615</v>
+        <v>50.361499999999999</v>
       </c>
       <c r="O6">
-        <v>38.2739</v>
+        <v>38.273899999999998</v>
       </c>
       <c r="P6">
         <v>125.3613</v>
       </c>
       <c r="Q6">
-        <v>69.80240000000001</v>
+        <v>69.802400000000006</v>
       </c>
       <c r="R6">
-        <v>27.1369</v>
+        <v>27.136900000000001</v>
       </c>
       <c r="S6">
-        <v>32.7644</v>
+        <v>32.764400000000002</v>
       </c>
       <c r="T6">
-        <v>33.6955</v>
+        <v>33.695500000000003</v>
       </c>
       <c r="U6">
         <v>0.1522</v>
@@ -1169,54 +1207,54 @@
         <v>-13.2324</v>
       </c>
       <c r="W6">
-        <v>20.2848</v>
+        <v>20.284800000000001</v>
       </c>
       <c r="X6">
-        <v>2.8078</v>
+        <v>2.8077999999999999</v>
       </c>
       <c r="Y6">
-        <v>-12.1918</v>
+        <v>-12.191800000000001</v>
       </c>
       <c r="Z6">
         <v>-13.2324</v>
       </c>
       <c r="AA6">
-        <v>20.2848</v>
+        <v>20.284800000000001</v>
       </c>
       <c r="AB6">
-        <v>2.8078</v>
+        <v>2.8077999999999999</v>
       </c>
       <c r="AC6">
-        <v>-23.2335</v>
+        <v>-23.233499999999999</v>
       </c>
       <c r="AD6">
-        <v>157.3465</v>
+        <v>157.34649999999999</v>
       </c>
       <c r="AE6">
-        <v>-73.12049999999999</v>
+        <v>-73.120499999999993</v>
       </c>
       <c r="AF6">
-        <v>238.7771</v>
+        <v>238.77709999999999</v>
       </c>
       <c r="AG6">
         <v>27.25132801307241</v>
       </c>
       <c r="AH6">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AI6">
-        <v>27.25132801307977</v>
+        <v>27.251328013079771</v>
       </c>
       <c r="AJ6">
-        <v>12.96045708253608</v>
+        <v>12.960457082536079</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
       <c r="B7">
-        <v>1.282499999787149</v>
+        <v>1.2824999997871489</v>
       </c>
       <c r="C7">
         <v>0.25</v>
@@ -1228,37 +1266,37 @@
         <v>0.6774</v>
       </c>
       <c r="F7">
-        <v>1.0106</v>
+        <v>1.0105999999999999</v>
       </c>
       <c r="G7">
-        <v>9.656000000000001</v>
+        <v>9.6560000000000006</v>
       </c>
       <c r="H7">
-        <v>5.4243</v>
+        <v>5.4242999999999997</v>
       </c>
       <c r="I7">
         <v>0.6774</v>
       </c>
       <c r="J7">
-        <v>1.0106</v>
+        <v>1.0105999999999999</v>
       </c>
       <c r="K7">
-        <v>9.656000000000001</v>
+        <v>9.6560000000000006</v>
       </c>
       <c r="L7">
-        <v>5.4243</v>
+        <v>5.4242999999999997</v>
       </c>
       <c r="M7">
-        <v>0.4567</v>
+        <v>0.45669999999999999</v>
       </c>
       <c r="N7">
-        <v>0.9079</v>
+        <v>0.90790000000000004</v>
       </c>
       <c r="O7">
-        <v>16.5241</v>
+        <v>16.524100000000001</v>
       </c>
       <c r="P7">
-        <v>8.6388</v>
+        <v>8.6387999999999998</v>
       </c>
       <c r="Q7">
         <v>-1.3045</v>
@@ -1267,66 +1305,66 @@
         <v>-1.7198</v>
       </c>
       <c r="S7">
-        <v>10.5132</v>
+        <v>10.513199999999999</v>
       </c>
       <c r="T7">
-        <v>5.4658</v>
+        <v>5.4657999999999998</v>
       </c>
       <c r="U7">
         <v>-100.2474</v>
       </c>
       <c r="V7">
-        <v>-23.7904</v>
+        <v>-23.790400000000002</v>
       </c>
       <c r="W7">
-        <v>75.80289999999999</v>
+        <v>75.802899999999994</v>
       </c>
       <c r="X7">
-        <v>99.20740000000001</v>
+        <v>99.207400000000007</v>
       </c>
       <c r="Y7">
-        <v>-102.3315</v>
+        <v>-102.33150000000001</v>
       </c>
       <c r="Z7">
-        <v>-23.7904</v>
+        <v>-23.790400000000002</v>
       </c>
       <c r="AA7">
-        <v>75.80289999999999</v>
+        <v>75.802899999999994</v>
       </c>
       <c r="AB7">
-        <v>99.20740000000001</v>
+        <v>99.207400000000007</v>
       </c>
       <c r="AC7">
-        <v>1.688</v>
+        <v>1.6879999999999999</v>
       </c>
       <c r="AD7">
         <v>1.3646</v>
       </c>
       <c r="AE7">
-        <v>10.3334</v>
+        <v>10.333399999999999</v>
       </c>
       <c r="AF7">
-        <v>16.9808</v>
+        <v>16.980799999999999</v>
       </c>
       <c r="AG7">
-        <v>9.891328013076595</v>
+        <v>9.8913280130765955</v>
       </c>
       <c r="AH7">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
       <c r="AI7">
-        <v>11.17382801286374</v>
+        <v>11.173828012863741</v>
       </c>
       <c r="AJ7">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
       <c r="B8">
-        <v>3.800000000001056</v>
+        <v>3.8000000000010559</v>
       </c>
       <c r="C8">
         <v>0.25</v>
@@ -1335,108 +1373,108 @@
         <v>57</v>
       </c>
       <c r="E8">
-        <v>-3.3482</v>
+        <v>-3.3481999999999998</v>
       </c>
       <c r="F8">
-        <v>-5.8105</v>
+        <v>-5.8105000000000002</v>
       </c>
       <c r="G8">
-        <v>19.2948</v>
+        <v>19.294799999999999</v>
       </c>
       <c r="H8">
         <v>10.468</v>
       </c>
       <c r="I8">
-        <v>-3.3482</v>
+        <v>-3.3481999999999998</v>
       </c>
       <c r="J8">
-        <v>-5.8105</v>
+        <v>-5.8105000000000002</v>
       </c>
       <c r="K8">
-        <v>19.2948</v>
+        <v>19.294799999999999</v>
       </c>
       <c r="L8">
         <v>10.468</v>
       </c>
       <c r="M8">
-        <v>-1.3797</v>
+        <v>-1.3796999999999999</v>
       </c>
       <c r="N8">
-        <v>7.1279</v>
+        <v>7.1279000000000003</v>
       </c>
       <c r="O8">
-        <v>72.2021</v>
+        <v>72.202100000000002</v>
       </c>
       <c r="P8">
-        <v>97.04859999999999</v>
+        <v>97.048599999999993</v>
       </c>
       <c r="Q8">
-        <v>-10.0851</v>
+        <v>-10.085100000000001</v>
       </c>
       <c r="R8">
-        <v>-7.9795</v>
+        <v>-7.9794999999999998</v>
       </c>
       <c r="S8">
-        <v>32.249</v>
+        <v>32.249000000000002</v>
       </c>
       <c r="T8">
-        <v>79.76430000000001</v>
+        <v>79.764300000000006</v>
       </c>
       <c r="U8">
         <v>-312.6755</v>
       </c>
       <c r="V8">
-        <v>-77.0185</v>
+        <v>-77.018500000000003</v>
       </c>
       <c r="W8">
-        <v>181.0766</v>
+        <v>181.07660000000001</v>
       </c>
       <c r="X8">
         <v>156.9889</v>
       </c>
       <c r="Y8">
-        <v>-318.8505</v>
+        <v>-318.85050000000001</v>
       </c>
       <c r="Z8">
-        <v>-77.0185</v>
+        <v>-77.018500000000003</v>
       </c>
       <c r="AA8">
-        <v>181.0766</v>
+        <v>181.07660000000001</v>
       </c>
       <c r="AB8">
         <v>156.9889</v>
       </c>
       <c r="AC8">
-        <v>-9.1587</v>
+        <v>-9.1586999999999996</v>
       </c>
       <c r="AD8">
-        <v>5.748200000000001</v>
+        <v>5.7482000000000006</v>
       </c>
       <c r="AE8">
-        <v>-15.557075</v>
+        <v>-15.557074999999999</v>
       </c>
       <c r="AF8">
-        <v>-98.42829999999999</v>
+        <v>-98.428299999999993</v>
       </c>
       <c r="AG8">
-        <v>9.891328013073675</v>
+        <v>9.8913280130736752</v>
       </c>
       <c r="AH8">
-        <v>28.08040504428485</v>
+        <v>28.080405044284849</v>
       </c>
       <c r="AI8">
-        <v>9.891328013076595</v>
+        <v>9.8913280130765955</v>
       </c>
       <c r="AJ8">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
       <c r="B9">
-        <v>7.277525405395011</v>
+        <v>7.2775254053950107</v>
       </c>
       <c r="C9">
         <v>0.25</v>
@@ -1445,108 +1483,108 @@
         <v>57</v>
       </c>
       <c r="E9">
-        <v>-2.7276</v>
+        <v>-2.7275999999999998</v>
       </c>
       <c r="F9">
-        <v>-8.4778</v>
+        <v>-8.4778000000000002</v>
       </c>
       <c r="G9">
-        <v>5.1077</v>
+        <v>5.1077000000000004</v>
       </c>
       <c r="H9">
         <v>15.6112</v>
       </c>
       <c r="I9">
-        <v>-2.7276</v>
+        <v>-2.7275999999999998</v>
       </c>
       <c r="J9">
-        <v>-8.4778</v>
+        <v>-8.4778000000000002</v>
       </c>
       <c r="K9">
-        <v>5.1077</v>
+        <v>5.1077000000000004</v>
       </c>
       <c r="L9">
         <v>15.6112</v>
       </c>
       <c r="M9">
-        <v>-57.0829</v>
+        <v>-57.082900000000002</v>
       </c>
       <c r="N9">
-        <v>2.789</v>
+        <v>2.7890000000000001</v>
       </c>
       <c r="O9">
         <v>64.9846</v>
       </c>
       <c r="P9">
-        <v>624.0337</v>
+        <v>624.03369999999995</v>
       </c>
       <c r="Q9">
-        <v>-64.1746</v>
+        <v>-64.174599999999998</v>
       </c>
       <c r="R9">
-        <v>-19.2533</v>
+        <v>-19.253299999999999</v>
       </c>
       <c r="S9">
         <v>62.44</v>
       </c>
       <c r="T9">
-        <v>590.3302</v>
+        <v>590.33019999999999</v>
       </c>
       <c r="U9">
-        <v>-676.2804</v>
+        <v>-676.28039999999999</v>
       </c>
       <c r="V9">
-        <v>-168.2075</v>
+        <v>-168.20750000000001</v>
       </c>
       <c r="W9">
-        <v>69.9837</v>
+        <v>69.983699999999999</v>
       </c>
       <c r="X9">
         <v>158.822</v>
       </c>
       <c r="Y9">
-        <v>-688.1064</v>
+        <v>-688.10640000000001</v>
       </c>
       <c r="Z9">
-        <v>-168.2075</v>
+        <v>-168.20750000000001</v>
       </c>
       <c r="AA9">
-        <v>69.9837</v>
+        <v>69.983699999999999</v>
       </c>
       <c r="AB9">
         <v>158.822</v>
       </c>
       <c r="AC9">
-        <v>-11.2054</v>
+        <v>-11.205399999999999</v>
       </c>
       <c r="AD9">
-        <v>-57.0829</v>
+        <v>-57.082900000000002</v>
       </c>
       <c r="AE9">
-        <v>-20.79435</v>
+        <v>-20.794350000000001</v>
       </c>
       <c r="AF9">
-        <v>-681.1165999999999</v>
+        <v>-681.11659999999995</v>
       </c>
       <c r="AG9">
-        <v>15.51969870252299</v>
+        <v>15.519698702522991</v>
       </c>
       <c r="AH9">
         <v>24.67749258361787</v>
       </c>
       <c r="AI9">
-        <v>15.84141249198782</v>
+        <v>15.841412491987819</v>
       </c>
       <c r="AJ9">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
       <c r="B10">
-        <v>5.099953953965137</v>
+        <v>5.0999539539651373</v>
       </c>
       <c r="C10">
         <v>0.25</v>
@@ -1555,10 +1593,10 @@
         <v>58</v>
       </c>
       <c r="E10">
-        <v>-27.2143</v>
+        <v>-27.214300000000001</v>
       </c>
       <c r="F10">
-        <v>-8.623200000000001</v>
+        <v>-8.6232000000000006</v>
       </c>
       <c r="G10">
         <v>28.7636</v>
@@ -1567,10 +1605,10 @@
         <v>13.9832</v>
       </c>
       <c r="I10">
-        <v>-27.2143</v>
+        <v>-27.214300000000001</v>
       </c>
       <c r="J10">
-        <v>-8.623200000000001</v>
+        <v>-8.6232000000000006</v>
       </c>
       <c r="K10">
         <v>28.7636</v>
@@ -1582,81 +1620,81 @@
         <v>121.2713</v>
       </c>
       <c r="N10">
-        <v>31.4717</v>
+        <v>31.471699999999998</v>
       </c>
       <c r="O10">
         <v>243.2748</v>
       </c>
       <c r="P10">
-        <v>73.7625</v>
+        <v>73.762500000000003</v>
       </c>
       <c r="Q10">
-        <v>50.5142</v>
+        <v>50.514200000000002</v>
       </c>
       <c r="R10">
-        <v>9.051399999999999</v>
+        <v>9.0513999999999992</v>
       </c>
       <c r="S10">
-        <v>239.3701</v>
+        <v>239.37010000000001</v>
       </c>
       <c r="T10">
-        <v>39.5224</v>
+        <v>39.522399999999998</v>
       </c>
       <c r="U10">
         <v>-145.9956</v>
       </c>
       <c r="V10">
-        <v>-38.2528</v>
+        <v>-38.252800000000001</v>
       </c>
       <c r="W10">
-        <v>60.7217</v>
+        <v>60.721699999999998</v>
       </c>
       <c r="X10">
-        <v>78.393</v>
+        <v>78.393000000000001</v>
       </c>
       <c r="Y10">
-        <v>-154.2831</v>
+        <v>-154.28309999999999</v>
       </c>
       <c r="Z10">
-        <v>-38.2528</v>
+        <v>-38.252800000000001</v>
       </c>
       <c r="AA10">
-        <v>60.7217</v>
+        <v>60.721699999999998</v>
       </c>
       <c r="AB10">
-        <v>78.393</v>
+        <v>78.393000000000001</v>
       </c>
       <c r="AC10">
-        <v>-35.83750000000001</v>
+        <v>-35.837500000000013</v>
       </c>
       <c r="AD10">
-        <v>152.743</v>
+        <v>152.74299999999999</v>
       </c>
       <c r="AE10">
-        <v>-55.97790000000001</v>
+        <v>-55.977900000000012</v>
       </c>
       <c r="AF10">
-        <v>364.5461</v>
+        <v>364.54610000000002</v>
       </c>
       <c r="AG10">
         <v>22.24946566955154</v>
       </c>
       <c r="AH10">
-        <v>28.64026302814882</v>
+        <v>28.640263028148819</v>
       </c>
       <c r="AI10">
         <v>17.14951171558641</v>
       </c>
       <c r="AJ10">
-        <v>28.64026302812646</v>
+        <v>28.640263028126459</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
       <c r="B11">
-        <v>4.909947961302368</v>
+        <v>4.9099479613023682</v>
       </c>
       <c r="C11">
         <v>0.25</v>
@@ -1665,58 +1703,58 @@
         <v>57</v>
       </c>
       <c r="E11">
-        <v>6.4747</v>
+        <v>6.4747000000000003</v>
       </c>
       <c r="F11">
-        <v>-2.9462</v>
+        <v>-2.9462000000000002</v>
       </c>
       <c r="G11">
-        <v>25.696</v>
+        <v>25.696000000000002</v>
       </c>
       <c r="H11">
         <v>23.8413</v>
       </c>
       <c r="I11">
-        <v>6.4747</v>
+        <v>6.4747000000000003</v>
       </c>
       <c r="J11">
-        <v>-2.9462</v>
+        <v>-2.9462000000000002</v>
       </c>
       <c r="K11">
-        <v>25.696</v>
+        <v>25.696000000000002</v>
       </c>
       <c r="L11">
         <v>23.8413</v>
       </c>
       <c r="M11">
-        <v>-23.139</v>
+        <v>-23.138999999999999</v>
       </c>
       <c r="N11">
-        <v>2.2466</v>
+        <v>2.2465999999999999</v>
       </c>
       <c r="O11">
-        <v>121.6389</v>
+        <v>121.63890000000001</v>
       </c>
       <c r="P11">
         <v>257.3116</v>
       </c>
       <c r="Q11">
-        <v>-39.9734</v>
+        <v>-39.973399999999998</v>
       </c>
       <c r="R11">
         <v>-5.4135</v>
       </c>
       <c r="S11">
-        <v>56.1781</v>
+        <v>56.178100000000001</v>
       </c>
       <c r="T11">
-        <v>198.5956</v>
+        <v>198.59559999999999</v>
       </c>
       <c r="U11">
-        <v>-257.3633</v>
+        <v>-257.36329999999998</v>
       </c>
       <c r="V11">
-        <v>-71.51349999999999</v>
+        <v>-71.513499999999993</v>
       </c>
       <c r="W11">
         <v>238.636</v>
@@ -1725,10 +1763,10 @@
         <v>189.4435</v>
       </c>
       <c r="Y11">
-        <v>-265.342</v>
+        <v>-265.34199999999998</v>
       </c>
       <c r="Z11">
-        <v>-71.51349999999999</v>
+        <v>-71.513499999999993</v>
       </c>
       <c r="AA11">
         <v>238.636</v>
@@ -1737,19 +1775,19 @@
         <v>189.4435</v>
       </c>
       <c r="AC11">
-        <v>6.4747</v>
+        <v>6.4747000000000003</v>
       </c>
       <c r="AD11">
-        <v>-23.139</v>
+        <v>-23.138999999999999</v>
       </c>
       <c r="AE11">
-        <v>30.316</v>
+        <v>30.315999999999999</v>
       </c>
       <c r="AF11">
-        <v>-280.4506</v>
+        <v>-280.45060000000001</v>
       </c>
       <c r="AG11">
-        <v>22.24946566955157</v>
+        <v>22.249465669551569</v>
       </c>
       <c r="AH11">
         <v>27.07045708295799</v>
@@ -1758,15 +1796,15 @@
         <v>22.24946566955154</v>
       </c>
       <c r="AJ11">
-        <v>31.98040504426036</v>
+        <v>31.980405044260358</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
       <c r="B12">
-        <v>2.521175053554387</v>
+        <v>2.5211750535543871</v>
       </c>
       <c r="C12">
         <v>0.25</v>
@@ -1778,46 +1816,46 @@
         <v>-2.9777</v>
       </c>
       <c r="F12">
-        <v>-0.1626</v>
+        <v>-0.16259999999999999</v>
       </c>
       <c r="G12">
         <v>11.2979</v>
       </c>
       <c r="H12">
-        <v>5.9106</v>
+        <v>5.9105999999999996</v>
       </c>
       <c r="I12">
         <v>-2.9777</v>
       </c>
       <c r="J12">
-        <v>-0.1626</v>
+        <v>-0.16259999999999999</v>
       </c>
       <c r="K12">
         <v>11.2979</v>
       </c>
       <c r="L12">
-        <v>5.9106</v>
+        <v>5.9105999999999996</v>
       </c>
       <c r="M12">
-        <v>4.5976</v>
+        <v>4.5975999999999999</v>
       </c>
       <c r="N12">
-        <v>-0.4144</v>
+        <v>-0.41439999999999999</v>
       </c>
       <c r="O12">
-        <v>51.9841</v>
+        <v>51.984099999999998</v>
       </c>
       <c r="P12">
         <v>15.52</v>
       </c>
       <c r="Q12">
-        <v>-3.1445</v>
+        <v>-3.1444999999999999</v>
       </c>
       <c r="R12">
-        <v>-0.8371</v>
+        <v>-0.83709999999999996</v>
       </c>
       <c r="S12">
-        <v>31.9049</v>
+        <v>31.904900000000001</v>
       </c>
       <c r="T12">
         <v>1.5723</v>
@@ -1826,57 +1864,57 @@
         <v>-129.5146</v>
       </c>
       <c r="V12">
-        <v>-33.6911</v>
+        <v>-33.691099999999999</v>
       </c>
       <c r="W12">
         <v>62.8994</v>
       </c>
       <c r="X12">
-        <v>29.4812</v>
+        <v>29.481200000000001</v>
       </c>
       <c r="Y12">
-        <v>-133.6115</v>
+        <v>-133.61150000000001</v>
       </c>
       <c r="Z12">
-        <v>-33.6911</v>
+        <v>-33.691099999999999</v>
       </c>
       <c r="AA12">
         <v>62.8994</v>
       </c>
       <c r="AB12">
-        <v>29.4812</v>
+        <v>29.481200000000001</v>
       </c>
       <c r="AC12">
-        <v>-3.1403</v>
+        <v>-3.1402999999999999</v>
       </c>
       <c r="AD12">
-        <v>4.5976</v>
+        <v>4.5975999999999999</v>
       </c>
       <c r="AE12">
-        <v>-14.2756</v>
+        <v>-14.275600000000001</v>
       </c>
       <c r="AF12">
-        <v>56.5817</v>
+        <v>56.581699999999998</v>
       </c>
       <c r="AG12">
-        <v>9.891328013073675</v>
+        <v>9.8913280130736752</v>
       </c>
       <c r="AH12">
-        <v>25.52483099643758</v>
+        <v>25.524830996437579</v>
       </c>
       <c r="AI12">
         <v>12.41250306662806</v>
       </c>
       <c r="AJ12">
-        <v>25.5248309964259</v>
+        <v>25.524830996425901</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
       <c r="B13">
-        <v>5.19999999998649</v>
+        <v>5.1999999999864901</v>
       </c>
       <c r="C13">
         <v>0.25</v>
@@ -1885,103 +1923,103 @@
         <v>58</v>
       </c>
       <c r="E13">
-        <v>8.0745</v>
+        <v>8.0745000000000005</v>
       </c>
       <c r="F13">
-        <v>4.4994</v>
+        <v>4.4993999999999996</v>
       </c>
       <c r="G13">
         <v>29.2864</v>
       </c>
       <c r="H13">
-        <v>12.0056</v>
+        <v>12.005599999999999</v>
       </c>
       <c r="I13">
-        <v>8.0745</v>
+        <v>8.0745000000000005</v>
       </c>
       <c r="J13">
-        <v>4.4994</v>
+        <v>4.4993999999999996</v>
       </c>
       <c r="K13">
         <v>29.2864</v>
       </c>
       <c r="L13">
-        <v>12.0056</v>
+        <v>12.005599999999999</v>
       </c>
       <c r="M13">
-        <v>-33.7795</v>
+        <v>-33.779499999999999</v>
       </c>
       <c r="N13">
-        <v>-13.5384</v>
+        <v>-13.538399999999999</v>
       </c>
       <c r="O13">
-        <v>396.7809</v>
+        <v>396.78089999999997</v>
       </c>
       <c r="P13">
-        <v>80.8486</v>
+        <v>80.848600000000005</v>
       </c>
       <c r="Q13">
-        <v>-54.7731</v>
+        <v>-54.773099999999999</v>
       </c>
       <c r="R13">
-        <v>-25.2368</v>
+        <v>-25.236799999999999</v>
       </c>
       <c r="S13">
-        <v>349.5824</v>
+        <v>349.58240000000001</v>
       </c>
       <c r="T13">
-        <v>51.892</v>
+        <v>51.892000000000003</v>
       </c>
       <c r="U13">
-        <v>-455.1483</v>
+        <v>-455.14830000000001</v>
       </c>
       <c r="V13">
-        <v>-110.9467</v>
+        <v>-110.94670000000001</v>
       </c>
       <c r="W13">
-        <v>228.2617</v>
+        <v>228.26169999999999</v>
       </c>
       <c r="X13">
-        <v>63.9528</v>
+        <v>63.952800000000003</v>
       </c>
       <c r="Y13">
-        <v>-463.5983</v>
+        <v>-463.59829999999999</v>
       </c>
       <c r="Z13">
-        <v>-110.9467</v>
+        <v>-110.94670000000001</v>
       </c>
       <c r="AA13">
-        <v>228.2617</v>
+        <v>228.26169999999999</v>
       </c>
       <c r="AB13">
-        <v>63.9528</v>
+        <v>63.952800000000003</v>
       </c>
       <c r="AC13">
         <v>12.5739</v>
       </c>
       <c r="AD13">
-        <v>-47.31789999999999</v>
+        <v>-47.317899999999987</v>
       </c>
       <c r="AE13">
-        <v>37.3609</v>
+        <v>37.360900000000001</v>
       </c>
       <c r="AF13">
-        <v>-430.5604</v>
+        <v>-430.56040000000002</v>
       </c>
       <c r="AG13">
-        <v>15.09132801306997</v>
+        <v>15.091328013069971</v>
       </c>
       <c r="AH13">
-        <v>22.91045708266948</v>
+        <v>22.910457082669481</v>
       </c>
       <c r="AI13">
-        <v>9.891328013083479</v>
+        <v>9.8913280130834789</v>
       </c>
       <c r="AJ13">
-        <v>22.91045708266932</v>
+        <v>22.910457082669321</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -1995,108 +2033,108 @@
         <v>57</v>
       </c>
       <c r="E14">
-        <v>-0.7585</v>
+        <v>-0.75849999999999995</v>
       </c>
       <c r="F14">
-        <v>-8.6068</v>
+        <v>-8.6067999999999998</v>
       </c>
       <c r="G14">
-        <v>6.5387</v>
+        <v>6.5387000000000004</v>
       </c>
       <c r="H14">
-        <v>19.6073</v>
+        <v>19.607299999999999</v>
       </c>
       <c r="I14">
-        <v>-0.7585</v>
+        <v>-0.75849999999999995</v>
       </c>
       <c r="J14">
-        <v>-8.6068</v>
+        <v>-8.6067999999999998</v>
       </c>
       <c r="K14">
-        <v>6.5387</v>
+        <v>6.5387000000000004</v>
       </c>
       <c r="L14">
-        <v>19.6073</v>
+        <v>19.607299999999999</v>
       </c>
       <c r="M14">
-        <v>18.6741</v>
+        <v>18.674099999999999</v>
       </c>
       <c r="N14">
-        <v>13.8631</v>
+        <v>13.863099999999999</v>
       </c>
       <c r="O14">
-        <v>163.5287</v>
+        <v>163.52869999999999</v>
       </c>
       <c r="P14">
         <v>122.806</v>
       </c>
       <c r="Q14">
-        <v>16.7018</v>
+        <v>16.701799999999999</v>
       </c>
       <c r="R14">
-        <v>-8.514699999999999</v>
+        <v>-8.5146999999999995</v>
       </c>
       <c r="S14">
         <v>159.3021</v>
       </c>
       <c r="T14">
-        <v>86.7354</v>
+        <v>86.735399999999998</v>
       </c>
       <c r="U14">
-        <v>-745.3561999999999</v>
+        <v>-745.35619999999994</v>
       </c>
       <c r="V14">
-        <v>-172.8576</v>
+        <v>-172.85759999999999</v>
       </c>
       <c r="W14">
-        <v>327.9884</v>
+        <v>327.98840000000001</v>
       </c>
       <c r="X14">
-        <v>35.7272</v>
+        <v>35.727200000000003</v>
       </c>
       <c r="Y14">
-        <v>-761.5574</v>
+        <v>-761.55740000000003</v>
       </c>
       <c r="Z14">
-        <v>-172.8576</v>
+        <v>-172.85759999999999</v>
       </c>
       <c r="AA14">
-        <v>327.9884</v>
+        <v>327.98840000000001</v>
       </c>
       <c r="AB14">
-        <v>35.7272</v>
+        <v>35.727200000000003</v>
       </c>
       <c r="AC14">
-        <v>-9.3653</v>
+        <v>-9.3652999999999995</v>
       </c>
       <c r="AD14">
-        <v>32.5372</v>
+        <v>32.537199999999999</v>
       </c>
       <c r="AE14">
-        <v>-21.919075</v>
+        <v>-21.919074999999999</v>
       </c>
       <c r="AF14">
-        <v>141.4801</v>
+        <v>141.48009999999999</v>
       </c>
       <c r="AG14">
         <v>15.09132801307441</v>
       </c>
       <c r="AH14">
-        <v>23.78045708241964</v>
+        <v>23.780457082419641</v>
       </c>
       <c r="AI14">
         <v>15.09132801307441</v>
       </c>
       <c r="AJ14">
-        <v>21.38045708267161</v>
+        <v>21.380457082671612</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>49</v>
       </c>
       <c r="B15">
-        <v>5.55813765648135</v>
+        <v>5.5581376564813496</v>
       </c>
       <c r="C15">
         <v>0.25</v>
@@ -2108,105 +2146,105 @@
         <v>-12.2362</v>
       </c>
       <c r="F15">
-        <v>-3.9707</v>
+        <v>-3.9706999999999999</v>
       </c>
       <c r="G15">
         <v>30.9407</v>
       </c>
       <c r="H15">
-        <v>18.0257</v>
+        <v>18.025700000000001</v>
       </c>
       <c r="I15">
         <v>-12.2362</v>
       </c>
       <c r="J15">
-        <v>-3.9707</v>
+        <v>-3.9706999999999999</v>
       </c>
       <c r="K15">
         <v>30.9407</v>
       </c>
       <c r="L15">
-        <v>18.0257</v>
+        <v>18.025700000000001</v>
       </c>
       <c r="M15">
-        <v>56.3987</v>
+        <v>56.398699999999998</v>
       </c>
       <c r="N15">
-        <v>17.1413</v>
+        <v>17.141300000000001</v>
       </c>
       <c r="O15">
         <v>466.8184</v>
       </c>
       <c r="P15">
-        <v>139.3225</v>
+        <v>139.32249999999999</v>
       </c>
       <c r="Q15">
-        <v>24.5845</v>
+        <v>24.584499999999998</v>
       </c>
       <c r="R15">
-        <v>6.8174</v>
+        <v>6.8174000000000001</v>
       </c>
       <c r="S15">
-        <v>421.2031</v>
+        <v>421.20310000000001</v>
       </c>
       <c r="T15">
-        <v>92.59529999999999</v>
+        <v>92.595299999999995</v>
       </c>
       <c r="U15">
-        <v>-471.5239</v>
+        <v>-471.52390000000003</v>
       </c>
       <c r="V15">
-        <v>-110.5691</v>
+        <v>-110.56910000000001</v>
       </c>
       <c r="W15">
-        <v>179.7207</v>
+        <v>179.72069999999999</v>
       </c>
       <c r="X15">
         <v>51.6858</v>
       </c>
       <c r="Y15">
-        <v>-480.5559</v>
+        <v>-480.55590000000001</v>
       </c>
       <c r="Z15">
-        <v>-110.5691</v>
+        <v>-110.56910000000001</v>
       </c>
       <c r="AA15">
-        <v>179.7207</v>
+        <v>179.72069999999999</v>
       </c>
       <c r="AB15">
         <v>51.6858</v>
       </c>
       <c r="AC15">
-        <v>-16.2069</v>
+        <v>-16.206900000000001</v>
       </c>
       <c r="AD15">
-        <v>73.53999999999999</v>
+        <v>73.539999999999992</v>
       </c>
       <c r="AE15">
-        <v>-43.1769</v>
+        <v>-43.176900000000003</v>
       </c>
       <c r="AF15">
-        <v>523.2171</v>
+        <v>523.21709999999996</v>
       </c>
       <c r="AG15">
-        <v>17.04951171545635</v>
+        <v>17.049511715456351</v>
       </c>
       <c r="AH15">
         <v>23.23045708254595</v>
       </c>
       <c r="AI15">
-        <v>22.24946566955317</v>
+        <v>22.249465669553171</v>
       </c>
       <c r="AJ15">
         <v>23.23045708254595</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>50</v>
       </c>
       <c r="B16">
-        <v>3.269999999945643</v>
+        <v>3.2699999999456431</v>
       </c>
       <c r="C16">
         <v>0.25</v>
@@ -2218,105 +2256,105 @@
         <v>-1.4415</v>
       </c>
       <c r="F16">
-        <v>-3.0757</v>
+        <v>-3.0756999999999999</v>
       </c>
       <c r="G16">
         <v>1.7436</v>
       </c>
       <c r="H16">
-        <v>7.001</v>
+        <v>7.0010000000000003</v>
       </c>
       <c r="I16">
         <v>-1.4415</v>
       </c>
       <c r="J16">
-        <v>-3.0757</v>
+        <v>-3.0756999999999999</v>
       </c>
       <c r="K16">
         <v>1.7436</v>
       </c>
       <c r="L16">
-        <v>7.001</v>
+        <v>7.0010000000000003</v>
       </c>
       <c r="M16">
-        <v>-3.1642</v>
+        <v>-3.1642000000000001</v>
       </c>
       <c r="N16">
-        <v>2.018</v>
+        <v>2.0179999999999998</v>
       </c>
       <c r="O16">
-        <v>14.658</v>
+        <v>14.657999999999999</v>
       </c>
       <c r="P16">
-        <v>65.2131</v>
+        <v>65.213099999999997</v>
       </c>
       <c r="Q16">
-        <v>-6.9121</v>
+        <v>-6.9120999999999997</v>
       </c>
       <c r="R16">
-        <v>-5.9789</v>
+        <v>-5.9789000000000003</v>
       </c>
       <c r="S16">
         <v>11.833</v>
       </c>
       <c r="T16">
-        <v>48.1195</v>
+        <v>48.119500000000002</v>
       </c>
       <c r="U16">
         <v>-259.2312</v>
       </c>
       <c r="V16">
-        <v>-60.2466</v>
+        <v>-60.246600000000001</v>
       </c>
       <c r="W16">
-        <v>147.5245</v>
+        <v>147.52449999999999</v>
       </c>
       <c r="X16">
-        <v>46.8816</v>
+        <v>46.881599999999999</v>
       </c>
       <c r="Y16">
-        <v>-264.5449</v>
+        <v>-264.54489999999998</v>
       </c>
       <c r="Z16">
-        <v>-60.2466</v>
+        <v>-60.246600000000001</v>
       </c>
       <c r="AA16">
-        <v>147.5245</v>
+        <v>147.52449999999999</v>
       </c>
       <c r="AB16">
-        <v>46.8816</v>
+        <v>46.881599999999999</v>
       </c>
       <c r="AC16">
-        <v>-4.5172</v>
+        <v>-4.5171999999999999</v>
       </c>
       <c r="AD16">
-        <v>-3.1642</v>
+        <v>-3.1642000000000001</v>
       </c>
       <c r="AE16">
-        <v>-8.999025</v>
+        <v>-8.9990249999999996</v>
       </c>
       <c r="AF16">
-        <v>-68.37729999999999</v>
+        <v>-68.377299999999991</v>
       </c>
       <c r="AG16">
         <v>17.04951171545224</v>
       </c>
       <c r="AH16">
-        <v>20.50996836936585</v>
+        <v>20.509968369365851</v>
       </c>
       <c r="AI16">
         <v>16.69132801319839</v>
       </c>
       <c r="AJ16">
-        <v>23.7799683693115</v>
+        <v>23.779968369311501</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>51</v>
       </c>
       <c r="B17">
-        <v>5.200000000008435</v>
+        <v>5.2000000000084352</v>
       </c>
       <c r="C17">
         <v>0.25</v>
@@ -2325,91 +2363,91 @@
         <v>58</v>
       </c>
       <c r="E17">
-        <v>11.6826</v>
+        <v>11.682600000000001</v>
       </c>
       <c r="F17">
-        <v>6.7498</v>
+        <v>6.7497999999999996</v>
       </c>
       <c r="G17">
         <v>14.5946</v>
       </c>
       <c r="H17">
-        <v>3.0297</v>
+        <v>3.0297000000000001</v>
       </c>
       <c r="I17">
-        <v>11.6826</v>
+        <v>11.682600000000001</v>
       </c>
       <c r="J17">
-        <v>6.7498</v>
+        <v>6.7497999999999996</v>
       </c>
       <c r="K17">
         <v>14.5946</v>
       </c>
       <c r="L17">
-        <v>3.0297</v>
+        <v>3.0297000000000001</v>
       </c>
       <c r="M17">
-        <v>-40.8195</v>
+        <v>-40.819499999999998</v>
       </c>
       <c r="N17">
         <v>-14.5589</v>
       </c>
       <c r="O17">
-        <v>348.8312</v>
+        <v>348.83120000000002</v>
       </c>
       <c r="P17">
-        <v>20.2189</v>
+        <v>20.218900000000001</v>
       </c>
       <c r="Q17">
-        <v>-71.1943</v>
+        <v>-71.194299999999998</v>
       </c>
       <c r="R17">
         <v>-32.1083</v>
       </c>
       <c r="S17">
-        <v>338.6107</v>
+        <v>338.61070000000001</v>
       </c>
       <c r="T17">
         <v>13.9335</v>
       </c>
       <c r="U17">
-        <v>-455.2161</v>
+        <v>-455.21609999999998</v>
       </c>
       <c r="V17">
         <v>-119.3737</v>
       </c>
       <c r="W17">
-        <v>274.9476</v>
+        <v>274.94760000000002</v>
       </c>
       <c r="X17">
         <v>12.9598</v>
       </c>
       <c r="Y17">
-        <v>-463.6661</v>
+        <v>-463.66609999999997</v>
       </c>
       <c r="Z17">
         <v>-119.3737</v>
       </c>
       <c r="AA17">
-        <v>274.9476</v>
+        <v>274.94760000000002</v>
       </c>
       <c r="AB17">
         <v>12.9598</v>
       </c>
       <c r="AC17">
-        <v>18.4324</v>
+        <v>18.432400000000001</v>
       </c>
       <c r="AD17">
-        <v>-55.3784</v>
+        <v>-55.378399999999999</v>
       </c>
       <c r="AE17">
-        <v>27.6909</v>
+        <v>27.690899999999999</v>
       </c>
       <c r="AF17">
-        <v>-389.6507</v>
+        <v>-389.65069999999997</v>
       </c>
       <c r="AG17">
-        <v>15.09132801307137</v>
+        <v>15.091328013071371</v>
       </c>
       <c r="AH17">
         <v>17.71045708266114</v>
@@ -2421,12 +2459,12 @@
         <v>17.71045708266114</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>52</v>
       </c>
       <c r="B18">
-        <v>5.347632615672943</v>
+        <v>5.3476326156729428</v>
       </c>
       <c r="C18">
         <v>0.25</v>
@@ -2435,108 +2473,108 @@
         <v>58</v>
       </c>
       <c r="E18">
-        <v>9.058299999999999</v>
+        <v>9.0582999999999991</v>
       </c>
       <c r="F18">
         <v>1.3734</v>
       </c>
       <c r="G18">
-        <v>13.4212</v>
+        <v>13.421200000000001</v>
       </c>
       <c r="H18">
-        <v>6.6257</v>
+        <v>6.6257000000000001</v>
       </c>
       <c r="I18">
-        <v>9.058299999999999</v>
+        <v>9.0582999999999991</v>
       </c>
       <c r="J18">
         <v>1.3734</v>
       </c>
       <c r="K18">
-        <v>13.4212</v>
+        <v>13.421200000000001</v>
       </c>
       <c r="L18">
-        <v>6.6257</v>
+        <v>6.6257000000000001</v>
       </c>
       <c r="M18">
-        <v>-44.1989</v>
+        <v>-44.198900000000002</v>
       </c>
       <c r="N18">
-        <v>-6.6043</v>
+        <v>-6.6043000000000003</v>
       </c>
       <c r="O18">
         <v>333.3879</v>
       </c>
       <c r="P18">
-        <v>66.9217</v>
+        <v>66.921700000000001</v>
       </c>
       <c r="Q18">
-        <v>-67.7505</v>
+        <v>-67.750500000000002</v>
       </c>
       <c r="R18">
         <v>-10.1751</v>
       </c>
       <c r="S18">
-        <v>322.4458</v>
+        <v>322.44580000000002</v>
       </c>
       <c r="T18">
-        <v>50.1228</v>
+        <v>50.122799999999998</v>
       </c>
       <c r="U18">
-        <v>-224.7137</v>
+        <v>-224.71369999999999</v>
       </c>
       <c r="V18">
-        <v>-54.0355</v>
+        <v>-54.035499999999999</v>
       </c>
       <c r="W18">
         <v>47.942</v>
       </c>
       <c r="X18">
-        <v>154.7975</v>
+        <v>154.79750000000001</v>
       </c>
       <c r="Y18">
-        <v>-233.4036</v>
+        <v>-233.40360000000001</v>
       </c>
       <c r="Z18">
-        <v>-54.0355</v>
+        <v>-54.035499999999999</v>
       </c>
       <c r="AA18">
         <v>47.942</v>
       </c>
       <c r="AB18">
-        <v>154.7975</v>
+        <v>154.79750000000001</v>
       </c>
       <c r="AC18">
-        <v>10.4317</v>
+        <v>10.431699999999999</v>
       </c>
       <c r="AD18">
-        <v>-50.8032</v>
+        <v>-50.803199999999997</v>
       </c>
       <c r="AE18">
-        <v>22.4795</v>
+        <v>22.479500000000002</v>
       </c>
       <c r="AF18">
-        <v>-377.5868</v>
+        <v>-377.58679999999998</v>
       </c>
       <c r="AG18">
-        <v>18.82632801239999</v>
+        <v>18.826328012399991</v>
       </c>
       <c r="AH18">
         <v>19.46045708254109</v>
       </c>
       <c r="AI18">
-        <v>21.93896062887041</v>
+        <v>21.938960628870412</v>
       </c>
       <c r="AJ18">
         <v>19.46045708254109</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>53</v>
       </c>
       <c r="B19">
-        <v>5.347298337624352</v>
+        <v>5.3472983376243519</v>
       </c>
       <c r="C19">
         <v>0.25</v>
@@ -2545,103 +2583,103 @@
         <v>58</v>
       </c>
       <c r="E19">
-        <v>-0.6705</v>
+        <v>-0.67049999999999998</v>
       </c>
       <c r="F19">
-        <v>0.9424</v>
+        <v>0.94240000000000002</v>
       </c>
       <c r="G19">
-        <v>26.0298</v>
+        <v>26.029800000000002</v>
       </c>
       <c r="H19">
         <v>17.0077</v>
       </c>
       <c r="I19">
-        <v>-0.6705</v>
+        <v>-0.67049999999999998</v>
       </c>
       <c r="J19">
-        <v>0.9424</v>
+        <v>0.94240000000000002</v>
       </c>
       <c r="K19">
-        <v>26.0298</v>
+        <v>26.029800000000002</v>
       </c>
       <c r="L19">
         <v>17.0077</v>
       </c>
       <c r="M19">
-        <v>-16.274</v>
+        <v>-16.274000000000001</v>
       </c>
       <c r="N19">
         <v>-2.7081</v>
       </c>
       <c r="O19">
-        <v>446.9651</v>
+        <v>446.96510000000001</v>
       </c>
       <c r="P19">
-        <v>67.19329999999999</v>
+        <v>67.193299999999994</v>
       </c>
       <c r="Q19">
-        <v>-18.0173</v>
+        <v>-18.017299999999999</v>
       </c>
       <c r="R19">
-        <v>-5.1584</v>
+        <v>-5.1584000000000003</v>
       </c>
       <c r="S19">
-        <v>399.5884</v>
+        <v>399.58839999999998</v>
       </c>
       <c r="T19">
         <v>23.9298</v>
       </c>
       <c r="U19">
-        <v>-379.609</v>
+        <v>-379.60899999999998</v>
       </c>
       <c r="V19">
-        <v>-84.7304</v>
+        <v>-84.730400000000003</v>
       </c>
       <c r="W19">
-        <v>80.7488</v>
+        <v>80.748800000000003</v>
       </c>
       <c r="X19">
-        <v>99.3837</v>
+        <v>99.383700000000005</v>
       </c>
       <c r="Y19">
-        <v>-388.2984</v>
+        <v>-388.29840000000002</v>
       </c>
       <c r="Z19">
-        <v>-84.7304</v>
+        <v>-84.730400000000003</v>
       </c>
       <c r="AA19">
-        <v>80.7488</v>
+        <v>80.748800000000003</v>
       </c>
       <c r="AB19">
-        <v>99.3837</v>
+        <v>99.383700000000005</v>
       </c>
       <c r="AC19">
-        <v>-0.6705</v>
+        <v>-0.67049999999999998</v>
       </c>
       <c r="AD19">
-        <v>-18.9821</v>
+        <v>-18.982099999999999</v>
       </c>
       <c r="AE19">
-        <v>-26.7003</v>
+        <v>-26.700299999999999</v>
       </c>
       <c r="AF19">
-        <v>-463.2391</v>
+        <v>-463.23910000000001</v>
       </c>
       <c r="AG19">
-        <v>16.59132801319742</v>
+        <v>16.591328013197419</v>
       </c>
       <c r="AH19">
-        <v>15.76045708253501</v>
+        <v>15.760457082535011</v>
       </c>
       <c r="AI19">
-        <v>21.93862635082177</v>
+        <v>21.938626350821771</v>
       </c>
       <c r="AJ19">
         <v>15.7604570825407</v>
       </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -2655,108 +2693,108 @@
         <v>57</v>
       </c>
       <c r="E20">
-        <v>7.2934</v>
+        <v>7.2934000000000001</v>
       </c>
       <c r="F20">
         <v>-1.3471</v>
       </c>
       <c r="G20">
-        <v>7.1408</v>
+        <v>7.1407999999999996</v>
       </c>
       <c r="H20">
-        <v>6.4184</v>
+        <v>6.4184000000000001</v>
       </c>
       <c r="I20">
-        <v>7.2934</v>
+        <v>7.2934000000000001</v>
       </c>
       <c r="J20">
         <v>-1.3471</v>
       </c>
       <c r="K20">
-        <v>7.1408</v>
+        <v>7.1407999999999996</v>
       </c>
       <c r="L20">
-        <v>6.4184</v>
+        <v>6.4184000000000001</v>
       </c>
       <c r="M20">
-        <v>-14.6558</v>
+        <v>-14.655799999999999</v>
       </c>
       <c r="N20">
-        <v>-3.7997</v>
+        <v>-3.7997000000000001</v>
       </c>
       <c r="O20">
-        <v>22.6062</v>
+        <v>22.606200000000001</v>
       </c>
       <c r="P20">
-        <v>69.2698</v>
+        <v>69.269800000000004</v>
       </c>
       <c r="Q20">
-        <v>-33.6187</v>
+        <v>-33.618699999999997</v>
       </c>
       <c r="R20">
         <v>-7.3022</v>
       </c>
       <c r="S20">
-        <v>6.0701</v>
+        <v>6.0701000000000001</v>
       </c>
       <c r="T20">
-        <v>64.85250000000001</v>
+        <v>64.852500000000006</v>
       </c>
       <c r="U20">
         <v>-206.28</v>
       </c>
       <c r="V20">
-        <v>-46.3759</v>
+        <v>-46.375900000000001</v>
       </c>
       <c r="W20">
-        <v>36.3644</v>
+        <v>36.364400000000003</v>
       </c>
       <c r="X20">
-        <v>12.8191</v>
+        <v>12.819100000000001</v>
       </c>
       <c r="Y20">
-        <v>-212.2925</v>
+        <v>-212.29249999999999</v>
       </c>
       <c r="Z20">
-        <v>-46.3759</v>
+        <v>-46.375900000000001</v>
       </c>
       <c r="AA20">
-        <v>36.3644</v>
+        <v>36.364400000000003</v>
       </c>
       <c r="AB20">
-        <v>12.8191</v>
+        <v>12.819100000000001</v>
       </c>
       <c r="AC20">
-        <v>7.2934</v>
+        <v>7.2934000000000001</v>
       </c>
       <c r="AD20">
-        <v>-18.4555</v>
+        <v>-18.455500000000001</v>
       </c>
       <c r="AE20">
         <v>13.7118</v>
       </c>
       <c r="AF20">
-        <v>-83.9256</v>
+        <v>-83.925600000000003</v>
       </c>
       <c r="AG20">
-        <v>18.82632801240105</v>
+        <v>18.826328012401049</v>
       </c>
       <c r="AH20">
         <v>15.76045708254062</v>
       </c>
       <c r="AI20">
-        <v>18.82632801239999</v>
+        <v>18.826328012399991</v>
       </c>
       <c r="AJ20">
         <v>19.46045708254109</v>
       </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
       <c r="B21">
-        <v>4.220000017041452</v>
+        <v>4.2200000170414516</v>
       </c>
       <c r="C21">
         <v>0.25</v>
@@ -2768,10 +2806,10 @@
         <v>20.1401</v>
       </c>
       <c r="F21">
-        <v>1.9642</v>
+        <v>1.9641999999999999</v>
       </c>
       <c r="G21">
-        <v>13.6359</v>
+        <v>13.635899999999999</v>
       </c>
       <c r="H21">
         <v>27.8599</v>
@@ -2780,19 +2818,19 @@
         <v>20.1401</v>
       </c>
       <c r="J21">
-        <v>1.9642</v>
+        <v>1.9641999999999999</v>
       </c>
       <c r="K21">
-        <v>13.6359</v>
+        <v>13.635899999999999</v>
       </c>
       <c r="L21">
         <v>27.8599</v>
       </c>
       <c r="M21">
-        <v>-4.7388</v>
+        <v>-4.7388000000000003</v>
       </c>
       <c r="N21">
-        <v>-5.5901</v>
+        <v>-5.5900999999999996</v>
       </c>
       <c r="O21">
         <v>23.6282</v>
@@ -2801,72 +2839,72 @@
         <v>44.6753</v>
       </c>
       <c r="Q21">
-        <v>-57.103</v>
+        <v>-57.103000000000002</v>
       </c>
       <c r="R21">
-        <v>-10.6971</v>
+        <v>-10.697100000000001</v>
       </c>
       <c r="S21">
         <v>14.8871</v>
       </c>
       <c r="T21">
-        <v>29.7128</v>
+        <v>29.712800000000001</v>
       </c>
       <c r="U21">
         <v>-174.8869</v>
       </c>
       <c r="V21">
-        <v>-36.4481</v>
+        <v>-36.448099999999997</v>
       </c>
       <c r="W21">
-        <v>228.9505</v>
+        <v>228.95050000000001</v>
       </c>
       <c r="X21">
-        <v>18.4032</v>
+        <v>18.403199999999998</v>
       </c>
       <c r="Y21">
-        <v>-181.7444</v>
+        <v>-181.74440000000001</v>
       </c>
       <c r="Z21">
-        <v>-36.4481</v>
+        <v>-36.448099999999997</v>
       </c>
       <c r="AA21">
-        <v>228.9505</v>
+        <v>228.95050000000001</v>
       </c>
       <c r="AB21">
-        <v>18.4032</v>
+        <v>18.403199999999998</v>
       </c>
       <c r="AC21">
-        <v>22.1043</v>
+        <v>22.104299999999999</v>
       </c>
       <c r="AD21">
-        <v>-10.3289</v>
+        <v>-10.328900000000001</v>
       </c>
       <c r="AE21">
         <v>48</v>
       </c>
       <c r="AF21">
-        <v>-49.4141</v>
+        <v>-49.414099999999998</v>
       </c>
       <c r="AG21">
-        <v>21.93837338365771</v>
+        <v>21.938373383657709</v>
       </c>
       <c r="AH21">
-        <v>12.96045708253608</v>
+        <v>12.960457082536079</v>
       </c>
       <c r="AI21">
-        <v>21.93875464132435</v>
+        <v>21.938754641324351</v>
       </c>
       <c r="AJ21">
         <v>17.18045708235509</v>
       </c>
     </row>
-    <row r="22" spans="1:36">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
       <c r="B22">
-        <v>5.440000000037777</v>
+        <v>5.4400000000377773</v>
       </c>
       <c r="C22">
         <v>0.25</v>
@@ -2875,88 +2913,88 @@
         <v>57</v>
       </c>
       <c r="E22">
-        <v>-0.0608</v>
+        <v>-6.08E-2</v>
       </c>
       <c r="F22">
-        <v>-4.8977</v>
+        <v>-4.8977000000000004</v>
       </c>
       <c r="G22">
-        <v>4.8775</v>
+        <v>4.8775000000000004</v>
       </c>
       <c r="H22">
         <v>10.631</v>
       </c>
       <c r="I22">
-        <v>-0.0608</v>
+        <v>-6.08E-2</v>
       </c>
       <c r="J22">
-        <v>-4.8977</v>
+        <v>-4.8977000000000004</v>
       </c>
       <c r="K22">
-        <v>4.8775</v>
+        <v>4.8775000000000004</v>
       </c>
       <c r="L22">
         <v>10.631</v>
       </c>
       <c r="M22">
-        <v>-31.6075</v>
+        <v>-31.607500000000002</v>
       </c>
       <c r="N22">
-        <v>-2.4241</v>
+        <v>-2.4241000000000001</v>
       </c>
       <c r="O22">
-        <v>42.1696</v>
+        <v>42.169600000000003</v>
       </c>
       <c r="P22">
-        <v>265.1639</v>
+        <v>265.16390000000001</v>
       </c>
       <c r="Q22">
-        <v>-31.7656</v>
+        <v>-31.765599999999999</v>
       </c>
       <c r="R22">
-        <v>-15.1581</v>
+        <v>-15.158099999999999</v>
       </c>
       <c r="S22">
-        <v>38.2025</v>
+        <v>38.202500000000001</v>
       </c>
       <c r="T22">
-        <v>241.4052</v>
+        <v>241.40520000000001</v>
       </c>
       <c r="U22">
         <v>-402.3741</v>
       </c>
       <c r="V22">
-        <v>-96.2955</v>
+        <v>-96.295500000000004</v>
       </c>
       <c r="W22">
         <v>126.7467</v>
       </c>
       <c r="X22">
-        <v>13.681</v>
+        <v>13.680999999999999</v>
       </c>
       <c r="Y22">
-        <v>-411.2141</v>
+        <v>-411.21409999999997</v>
       </c>
       <c r="Z22">
-        <v>-96.2955</v>
+        <v>-96.295500000000004</v>
       </c>
       <c r="AA22">
         <v>126.7467</v>
       </c>
       <c r="AB22">
-        <v>13.681</v>
+        <v>13.680999999999999</v>
       </c>
       <c r="AC22">
-        <v>-4.958500000000001</v>
+        <v>-4.9585000000000008</v>
       </c>
       <c r="AD22">
-        <v>-34.0316</v>
+        <v>-34.031599999999997</v>
       </c>
       <c r="AE22">
-        <v>-11.707325</v>
+        <v>-11.707325000000001</v>
       </c>
       <c r="AF22">
-        <v>-296.7714</v>
+        <v>-296.77140000000003</v>
       </c>
       <c r="AG22">
         <v>15.09132801307441</v>
@@ -2968,7 +3006,7 @@
         <v>15.09132801307441</v>
       </c>
       <c r="AJ22">
-        <v>14.99045708264411</v>
+        <v>14.990457082644109</v>
       </c>
     </row>
   </sheetData>
